--- a/pages3/sources1.xlsx
+++ b/pages3/sources1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICT Project - marketplace\hello_layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815D2E38-007D-4FED-AAA0-7DD621B4E019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B0CA26-2832-46F5-AB48-8BC2C05A719F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{45C4181E-5654-41C3-B337-D42DCC1B202F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="87">
   <si>
     <t>Category</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Skirt</t>
   </si>
   <si>
-    <t>Size</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -280,6 +277,15 @@
   </si>
   <si>
     <t>IMAGES3/Lighter Blue Cutbray Jeans.png</t>
+  </si>
+  <si>
+    <t>Size 1</t>
+  </si>
+  <si>
+    <t>Size 2</t>
+  </si>
+  <si>
+    <t>Size 3</t>
   </si>
 </sst>
 </file>
@@ -312,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -346,57 +352,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -739,11 +705,15 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
@@ -753,22 +723,22 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4">
         <v>350000</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -776,22 +746,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4">
         <v>300000</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -799,22 +769,22 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4">
         <v>380000</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -822,22 +792,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4">
         <v>280000</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -845,22 +815,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="7">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4">
         <v>335000</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -868,22 +838,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="7">
+        <v>30</v>
+      </c>
+      <c r="C7" s="4">
         <v>450000</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -891,22 +861,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="7">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4">
         <v>320000</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -914,22 +884,22 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="7">
+        <v>39</v>
+      </c>
+      <c r="C9" s="4">
         <v>399000</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -937,22 +907,22 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="7">
+        <v>40</v>
+      </c>
+      <c r="C10" s="4">
         <v>250000</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -960,22 +930,22 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="7">
+        <v>41</v>
+      </c>
+      <c r="C11" s="4">
         <v>389000</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -983,22 +953,22 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="7">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4">
         <v>449000</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1006,22 +976,22 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="7">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4">
         <v>399000</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1029,22 +999,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="7">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4">
         <v>359000</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1052,22 +1022,22 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="7">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4">
         <v>329000</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -1075,22 +1045,22 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="7">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4">
         <v>295000</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1098,22 +1068,22 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="7">
+        <v>26</v>
+      </c>
+      <c r="C17" s="4">
         <v>299000</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -1121,22 +1091,22 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7">
+        <v>27</v>
+      </c>
+      <c r="C18" s="4">
         <v>395000</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1144,22 +1114,22 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4">
         <v>499000</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -1167,22 +1137,22 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="7">
+        <v>32</v>
+      </c>
+      <c r="C20" s="4">
         <v>299000</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1190,396 +1160,393 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="7">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4">
         <v>499000</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="8">
+        <v>14</v>
+      </c>
+      <c r="C22" s="5">
         <v>599000</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="7">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4">
         <v>499000</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="7">
+        <v>21</v>
+      </c>
+      <c r="C24" s="4">
         <v>399000</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="7">
+        <v>28</v>
+      </c>
+      <c r="C25" s="4">
         <v>449000</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="7">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4">
         <v>549000</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="7">
+        <v>31</v>
+      </c>
+      <c r="C27" s="4">
         <v>599000</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="7">
+        <v>34</v>
+      </c>
+      <c r="C28" s="4">
         <v>599000</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="7">
+        <v>35</v>
+      </c>
+      <c r="C29" s="4">
         <v>399000</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="8">
+        <v>36</v>
+      </c>
+      <c r="C30" s="5">
         <v>559000</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="7">
+        <v>37</v>
+      </c>
+      <c r="C31" s="4">
         <v>489000</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="7">
+        <v>42</v>
+      </c>
+      <c r="C32" s="4">
         <v>649000</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="7">
+        <v>43</v>
+      </c>
+      <c r="C33" s="4">
         <v>649000</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="7">
+        <v>44</v>
+      </c>
+      <c r="C34" s="4">
         <v>649000</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7">
+        <v>45</v>
+      </c>
+      <c r="C35" s="4">
         <v>649000</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="7">
+        <v>46</v>
+      </c>
+      <c r="C36" s="4">
         <v>699000</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="7">
+        <v>47</v>
+      </c>
+      <c r="C37" s="4">
         <v>699000</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages3/sources1.xlsx
+++ b/pages3/sources1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICT Project - marketplace\hello_layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B0CA26-2832-46F5-AB48-8BC2C05A719F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F93446-0C0C-42C4-BC5B-9AFDD65AFF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{45C4181E-5654-41C3-B337-D42DCC1B202F}"/>
   </bookViews>
@@ -279,13 +279,13 @@
     <t>IMAGES3/Lighter Blue Cutbray Jeans.png</t>
   </si>
   <si>
-    <t>Size 1</t>
-  </si>
-  <si>
-    <t>Size 2</t>
-  </si>
-  <si>
-    <t>Size 3</t>
+    <t>Size1</t>
+  </si>
+  <si>
+    <t>Size2</t>
+  </si>
+  <si>
+    <t>Size3</t>
   </si>
 </sst>
 </file>
